--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104551_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104551_W11.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9629</v>
+        <v>7.14</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6075</v>
+        <v>3.0315</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3554</v>
+        <v>4.1086</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.8369</v>
+        <v>-2.8547</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.1914</v>
+        <v>-3.2154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.9875</v>
+        <v>-2.0249</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.7338</v>
+        <v>-2.7696</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8494</v>
+        <v>-0.8298</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P2" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5768</v>
+        <v>1.7639</v>
       </c>
       <c r="T2" t="n">
-        <v>5.317</v>
+        <v>1.7879</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2598</v>
+        <v>-0.024</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8205</v>
+        <v>4.8163</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5425</v>
+        <v>1.5479</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3914</v>
+        <v>3.8096</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9218</v>
+        <v>2.3853</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4696</v>
+        <v>1.4242</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1613</v>
+        <v>1.1642</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9524</v>
+        <v>-0.948</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1138</v>
+        <v>2.1122</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6885</v>
+        <v>1.6797</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5272</v>
+        <v>-0.5155</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4815</v>
+        <v>0.8942</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2994</v>
+        <v>0.7755</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8114</v>
+        <v>2.2089</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0065</v>
+        <v>4.4642</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.195</v>
+        <v>-2.2553</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1741</v>
+        <v>-0.4755</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6508</v>
+        <v>-0.7002</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4767</v>
+        <v>0.2247</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0416</v>
+        <v>1.1728</v>
       </c>
       <c r="K4" t="n">
-        <v>1.967</v>
+        <v>0.4062</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8675</v>
+        <v>-1.6483</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3162</v>
+        <v>-1.1064</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5513</v>
+        <v>-0.5419</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>1.73</v>
+        <v>0.1381</v>
       </c>
       <c r="T4" t="n">
-        <v>2.099</v>
+        <v>0.5269</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.369</v>
+        <v>-0.3888</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>1.8634</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>4.3579</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.639</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7745</v>
+        <v>1.4498</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9025</v>
+        <v>1.998</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.128</v>
+        <v>-0.5481</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0183</v>
+        <v>0.0164</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8282</v>
+        <v>1.8294</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8099</v>
+        <v>-1.813</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5236</v>
+        <v>1.5056</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5053</v>
+        <v>-1.4891</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0169</v>
+        <v>-0.339</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U5" t="n">
-        <v>0.47</v>
+        <v>0.0305</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.128</v>
+        <v>0.9829</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4517</v>
+        <v>-0.5858</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3237</v>
+        <v>1.5687</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4604</v>
+        <v>-2.4084</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6896</v>
+        <v>0.5833</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2292</v>
+        <v>-2.9917</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2072</v>
+        <v>-1.3774</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4289</v>
+        <v>1.2303</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7782</v>
+        <v>-2.6077</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6675</v>
+        <v>-1.031</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1185</v>
+        <v>-0.6471</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.549</v>
+        <v>-0.384</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>3.4145</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.956</v>
+        <v>0.8466</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5383</v>
+        <v>0.9588</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4177</v>
+        <v>-0.1122</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8639</v>
+        <v>1.6342</v>
       </c>
       <c r="W6" t="n">
-        <v>4.3707</v>
+        <v>2.3367</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5068</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1492</v>
+        <v>0.7589</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0592</v>
+        <v>3.93</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09</v>
+        <v>-3.1711</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.304</v>
+        <v>0.1772</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7778</v>
+        <v>1.6487</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0818</v>
+        <v>-1.4715</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1292</v>
+        <v>2.0255</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4014</v>
+        <v>1.951</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5306</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1749</v>
+        <v>-1.8483</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3764</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0931</v>
+        <v>0.6712</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4567</v>
+        <v>1.0426</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5498</v>
+        <v>-0.3714</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1079</v>
+        <v>0.6221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9058</v>
+        <v>0.2616</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0137</v>
+        <v>0.3605</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-1.3174</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0361</v>
+        <v>0.7729</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9649</v>
+        <v>-2.0903</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="K8" t="n">
-        <v>0.052</v>
+        <v>0.3857</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.749</v>
+        <v>-0.5443</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2318</v>
+        <v>-1.1588</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0159</v>
+        <v>0.3871</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2159</v>
+        <v>-1.546</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3242</v>
+        <v>0.3948</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0.6965</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1155</v>
+        <v>-0.3017</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.491</v>
+        <v>0.2922</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3042</v>
+        <v>-0.7914</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8132</v>
+        <v>1.0835</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3928</v>
+        <v>-0.9296</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5873</v>
+        <v>0.0373</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9802</v>
+        <v>-0.9668</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3385</v>
+        <v>-0.7007</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2499</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.5884</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0543</v>
+        <v>-0.2289</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6626</v>
+        <v>-0.0144</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3918</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.4025</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6445</v>
+        <v>-0.144</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8166</v>
+        <v>-0.0907</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1721</v>
+        <v>-0.0534</v>
       </c>
       <c r="V9" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4411</v>
+        <v>-0.5854</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4148</v>
+        <v>0.7178</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8559</v>
+        <v>-1.3032</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2354</v>
+        <v>-1.5954</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8485</v>
+        <v>-2.367</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6131</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9893999999999999</v>
+        <v>-0.392</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5817</v>
+        <v>-1.3897</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4078</v>
+        <v>0.9977</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.754</v>
+        <v>-1.2034</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2669</v>
+        <v>-0.9774</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0209</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4231</v>
+        <v>-0.3346</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3478</v>
+        <v>0.0902</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.4248</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9773</v>
+        <v>-0.999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3247</v>
+        <v>0.8716</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6526</v>
+        <v>-1.8706</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6049</v>
+        <v>0.2309</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3752</v>
+        <v>0.8446</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7703</v>
+        <v>-0.6138</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3774</v>
+        <v>0.974</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3822</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.0048</v>
+        <v>0.4019</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2275</v>
+        <v>-0.7432</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.993</v>
+        <v>0.2725</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2345</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7088</v>
+        <v>0.0174</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9739</v>
+        <v>0.1253</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7349</v>
+        <v>-0.1078</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2212</v>
+        <v>-2.6629</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2269</v>
+        <v>-2.8848</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0058</v>
+        <v>0.2219</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4488</v>
+        <v>-2.4388</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3666</v>
+        <v>-1.3589</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0822</v>
+        <v>-1.0799</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3276</v>
+        <v>-1.3352</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5786</v>
+        <v>-0.5828</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1212</v>
+        <v>-1.1036</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1995</v>
+        <v>-0.6597</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6611</v>
+        <v>-0.476</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7847</v>
+        <v>-4.5972</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4834</v>
+        <v>-4.5644</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3013</v>
+        <v>-0.0328</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7011</v>
+        <v>-2.6962</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7921</v>
+        <v>-1.7922</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9089</v>
+        <v>-0.904</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8835</v>
+        <v>-1.8952</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9954</v>
+        <v>-2.007</v>
       </c>
       <c r="L13" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2527</v>
+        <v>0.4436</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8026</v>
+        <v>0.7453</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5498</v>
+        <v>-0.3017</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.41</v>
+        <v>8.419899999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>9.119</v>
+        <v>8.833600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7088</v>
+        <v>-0.4137000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.0887</v>
+        <v>-13.1273</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.638599999999999</v>
+        <v>-4.665499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.4498</v>
+        <v>-8.461600000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2905000000000009</v>
+        <v>-0.5264000000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7693999999999999</v>
+        <v>-0.9250999999999996</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4790999999999994</v>
+        <v>0.3986</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.7982</v>
+        <v>-12.6008</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.8691</v>
+        <v>-3.7408</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.928999999999998</v>
+        <v>-8.860300000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3415</v>
+        <v>-11.3814</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5492</v>
+        <v>21.625</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6749</v>
+        <v>3.6925</v>
       </c>
       <c r="T14" t="n">
-        <v>6.064200000000001</v>
+        <v>6.105</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.3891</v>
+        <v>-2.4126</v>
       </c>
       <c r="V14" t="n">
-        <v>7.616300000000002</v>
+        <v>7.611600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>14.687</v>
+        <v>14.6365</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.0706</v>
+        <v>-7.024899999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3507</v>
+        <v>1.9896</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3934</v>
+        <v>1.8238</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0427</v>
+        <v>0.1659</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2725</v>
+        <v>3.0241</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7531</v>
+        <v>1.6566</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5194</v>
+        <v>1.3675</v>
       </c>
       <c r="J15" t="n">
-        <v>1.935</v>
+        <v>2.3035</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2211</v>
+        <v>0.71</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7139</v>
+        <v>1.5935</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3375</v>
+        <v>0.7206</v>
       </c>
       <c r="N15" t="n">
-        <v>0.532</v>
+        <v>0.9467</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1945</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-3.4145</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6372</v>
+        <v>-0.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4034</v>
+        <v>0.2111</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7661</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5591</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6429</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2019</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6939</v>
+        <v>1.6997</v>
       </c>
       <c r="E16" t="n">
-        <v>1.752</v>
+        <v>1.7616</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0581</v>
+        <v>-0.0619</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0708</v>
+        <v>2.2821</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3969</v>
+        <v>0.758</v>
       </c>
       <c r="I16" t="n">
-        <v>1.674</v>
+        <v>1.5241</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9443</v>
+        <v>1.9046</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1531</v>
+        <v>0.1994</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7912</v>
+        <v>1.7052</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.3775</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7563</v>
+        <v>0.5586</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1172</v>
+        <v>-0.1811</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-1.5934</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1766</v>
+        <v>-0.015</v>
       </c>
       <c r="T16" t="n">
-        <v>0.369</v>
+        <v>0.8194</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5456</v>
+        <v>-0.8344</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>-0.5674</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7071</v>
+        <v>0.6311</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5937</v>
+        <v>1.4535</v>
       </c>
       <c r="E17" t="n">
-        <v>1.742</v>
+        <v>1.3705</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1483</v>
+        <v>0.0829</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0137</v>
+        <v>2.068</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6462</v>
+        <v>0.3937</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3674</v>
+        <v>1.6743</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3221</v>
+        <v>2.9283</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7202</v>
+        <v>1.1409</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6019</v>
+        <v>1.7874</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6915</v>
+        <v>-0.8603</v>
       </c>
       <c r="N17" t="n">
-        <v>0.926</v>
+        <v>-0.7472</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2345</v>
+        <v>-0.113</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0174</v>
+        <v>-0.4065</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0907</v>
+        <v>0.0161</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1082</v>
+        <v>-0.4226</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>0.7025</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2686</v>
+        <v>0.6473</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5321</v>
+        <v>0.5657</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2635</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4142</v>
+        <v>3.4253</v>
       </c>
       <c r="H18" t="n">
-        <v>2.857</v>
+        <v>2.8604</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5572</v>
+        <v>0.5649</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5226</v>
+        <v>2.5047</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8915</v>
+        <v>0.9206</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5956</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.803</v>
+        <v>0.1732</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8903</v>
+        <v>0.952</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0873</v>
+        <v>-0.7788</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5876</v>
+        <v>-1.5854</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4779</v>
+        <v>0.4289</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8108</v>
+        <v>0.6725</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3329</v>
+        <v>-0.2436</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1134</v>
+        <v>-1.117</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.3231</v>
+        <v>-3.323</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2097</v>
+        <v>2.206</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5813</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2205</v>
+        <v>-2.231</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5321</v>
+        <v>-0.5168</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6179</v>
+        <v>0.5655</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>0.1833</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3185</v>
+        <v>0.3823</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4539</v>
+        <v>-0.2491</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4798</v>
+        <v>-0.2548</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0259</v>
+        <v>0.0057</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0372</v>
+        <v>1.0386</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8153</v>
+        <v>-0.8129</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8525</v>
+        <v>1.8515</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0022</v>
+        <v>0.995</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7539</v>
+        <v>1.7501</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0351</v>
+        <v>0.0437</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.65</v>
+        <v>-0.4471</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3021</v>
+        <v>-0.3355</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>M. THOMAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6157</v>
+        <v>-1.7468</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5206</v>
+        <v>-0.7209</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0951</v>
+        <v>-1.026</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9337</v>
+        <v>1.4492</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0722</v>
+        <v>3.0645</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1386</v>
+        <v>-1.6152</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1731</v>
+        <v>1.6325</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1358</v>
+        <v>3.1231</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>-1.4906</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2395</v>
+        <v>-0.1833</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0636</v>
+        <v>-0.0587</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1759</v>
+        <v>-0.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-3.8697</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3145</v>
+        <v>-0.1067</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4386</v>
+        <v>0.2691</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.124</v>
+        <v>-0.3758</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.9566</v>
+        <v>-1.0407</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7712</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. THOMAS</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8308</v>
+        <v>-3.0878</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6046</v>
+        <v>-1.0115</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2263</v>
+        <v>-2.0763</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4586</v>
+        <v>0.9336</v>
       </c>
       <c r="H22" t="n">
-        <v>3.0634</v>
+        <v>1.0659</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6047</v>
+        <v>-0.1323</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6757</v>
+        <v>1.1609</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1445</v>
+        <v>1.1236</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4689</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.217</v>
+        <v>-0.2273</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0578</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1359</v>
+        <v>-0.1695</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8562</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2068</v>
+        <v>-0.1579</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6775</v>
+        <v>-0.0327</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5293</v>
+        <v>-0.1253</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0412</v>
+        <v>-2.9529</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2946</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7281</v>
+        <v>-4.1966</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3578</v>
+        <v>-1.6778</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3704</v>
+        <v>-2.5187</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4696</v>
+        <v>0.4844</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6535</v>
+        <v>0.6629</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1839</v>
+        <v>-0.1785</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1206</v>
+        <v>-0.1376</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.603</v>
+        <v>-0.614</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="N23" t="n">
-        <v>1.2565</v>
+        <v>1.277</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.701</v>
+        <v>-1.1867</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>0.1019</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0931</v>
+        <v>-1.2885</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.909</v>
+        <v>-1.9009</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.0017</v>
+        <v>-2.9904</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1663</v>
+        <v>-4.5689</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5587</v>
+        <v>-2.1153</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6076</v>
+        <v>-2.4536</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4684</v>
+        <v>-0.4611</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6652</v>
+        <v>-1.6603</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1968</v>
+        <v>1.1992</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.075</v>
+        <v>-0.0906</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1917</v>
+        <v>-1.2001</v>
       </c>
       <c r="L24" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3935</v>
+        <v>-0.3704</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O24" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2957</v>
+        <v>-0.7014</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4688</v>
+        <v>0.0044</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8269</v>
+        <v>-0.7058</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5876</v>
+        <v>-1.5854</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.41</v>
+        <v>-7.630199999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7088000000000001</v>
+        <v>0.4137999999999993</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.119</v>
+        <v>-8.043999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>13.0885</v>
+        <v>13.1272</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6387</v>
+        <v>4.6658</v>
       </c>
       <c r="I25" t="n">
-        <v>8.449800000000002</v>
+        <v>8.461499999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>12.7981</v>
+        <v>12.601</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8692</v>
+        <v>3.7407</v>
       </c>
       <c r="L25" t="n">
-        <v>8.928900000000001</v>
+        <v>8.860099999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2901999999999998</v>
+        <v>0.5263000000000002</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7692999999999999</v>
+        <v>0.9248999999999998</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4792999999999999</v>
+        <v>-0.3984</v>
       </c>
       <c r="P25" t="n">
-        <v>-10.2074</v>
+        <v>-10.2434</v>
       </c>
       <c r="Q25" t="n">
-        <v>-21.5492</v>
+        <v>-21.625</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.6749</v>
+        <v>-2.9026</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3894</v>
+        <v>2.413</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.0641</v>
+        <v>-5.3155</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.6164</v>
+        <v>-7.611599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>7.070799999999999</v>
+        <v>7.0251</v>
       </c>
       <c r="X25" t="n">
-        <v>-14.6868</v>
+        <v>-14.6364</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104551_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104551_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>1.5479</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.024899999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.9904</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104551_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-14.6364</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
